--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Record</t>
   </si>
@@ -39,151 +39,157 @@
     <t>Junya Ettlinger's First Team</t>
   </si>
   <si>
+    <t>Serving Punt</t>
+  </si>
+  <si>
+    <t>Hall Pass</t>
+  </si>
+  <si>
+    <t>Ler and Order</t>
+  </si>
+  <si>
+    <t>Natural rack</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hunks of Hanet </t>
   </si>
   <si>
-    <t>Ler and Order</t>
-  </si>
-  <si>
-    <t>Natural rack</t>
-  </si>
-  <si>
-    <t>Serving Punt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jockstrap jubilee </t>
   </si>
   <si>
-    <t>Hall Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Case Closed </t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>95.6%</t>
-  </si>
-  <si>
-    <t>85.2%</t>
-  </si>
-  <si>
-    <t>66.9%</t>
-  </si>
-  <si>
-    <t>45.8%</t>
-  </si>
-  <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>33.2%</t>
-  </si>
-  <si>
-    <t>32.0%</t>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>98.6%</t>
+  </si>
+  <si>
+    <t>93.3%</t>
+  </si>
+  <si>
+    <t>88.3%</t>
+  </si>
+  <si>
+    <t>39.1%</t>
+  </si>
+  <si>
+    <t>37.2%</t>
+  </si>
+  <si>
+    <t>36.0%</t>
+  </si>
+  <si>
+    <t>7.9%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-2173</t>
-  </si>
-  <si>
-    <t>-576</t>
-  </si>
-  <si>
-    <t>-202</t>
-  </si>
-  <si>
-    <t>+118</t>
-  </si>
-  <si>
-    <t>+142</t>
-  </si>
-  <si>
-    <t>+201</t>
-  </si>
-  <si>
-    <t>+212</t>
-  </si>
-  <si>
-    <t>+∞</t>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-7043</t>
+  </si>
+  <si>
+    <t>-1393</t>
+  </si>
+  <si>
+    <t>-755</t>
+  </si>
+  <si>
+    <t>+156</t>
+  </si>
+  <si>
+    <t>+169</t>
+  </si>
+  <si>
+    <t>+178</t>
+  </si>
+  <si>
+    <t>+1166</t>
+  </si>
+  <si>
+    <t>+99900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>72.5%</t>
-  </si>
-  <si>
-    <t>25.5%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>81.2%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
+  </si>
+  <si>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>-432</t>
+  </si>
+  <si>
+    <t>+641</t>
+  </si>
+  <si>
+    <t>+2339</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>87.9%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>-264</t>
-  </si>
-  <si>
-    <t>+292</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>95.7%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-2226</t>
-  </si>
-  <si>
-    <t>+6150</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-726</t>
+  </si>
+  <si>
+    <t>+1199</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+9900</t>
   </si>
 </sst>
 </file>
@@ -566,10 +572,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -580,10 +586,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -594,10 +600,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -605,13 +611,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -622,10 +628,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -633,13 +639,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -650,10 +656,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -661,13 +667,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -675,13 +681,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -689,13 +695,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -724,30 +730,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -758,10 +764,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -769,24 +775,24 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>46</v>
@@ -794,16 +800,16 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -811,55 +817,55 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -891,111 +897,111 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1006,10 +1012,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1020,10 +1026,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -45,151 +45,151 @@
     <t>Hall Pass</t>
   </si>
   <si>
+    <t xml:space="preserve">Hunks of Hanet </t>
+  </si>
+  <si>
     <t>Ler and Order</t>
   </si>
   <si>
     <t>Natural rack</t>
   </si>
   <si>
-    <t xml:space="preserve">Hunks of Hanet </t>
+    <t xml:space="preserve">Case Closed </t>
   </si>
   <si>
     <t xml:space="preserve">Jockstrap jubilee </t>
   </si>
   <si>
-    <t xml:space="preserve">Case Closed </t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>98.6%</t>
-  </si>
-  <si>
-    <t>93.3%</t>
-  </si>
-  <si>
-    <t>88.3%</t>
-  </si>
-  <si>
-    <t>39.1%</t>
-  </si>
-  <si>
-    <t>37.2%</t>
-  </si>
-  <si>
-    <t>36.0%</t>
-  </si>
-  <si>
-    <t>7.9%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>93.6%</t>
+  </si>
+  <si>
+    <t>90.2%</t>
+  </si>
+  <si>
+    <t>82.4%</t>
+  </si>
+  <si>
+    <t>12.8%</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>7.1%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-1462</t>
+  </si>
+  <si>
+    <t>-920</t>
+  </si>
+  <si>
+    <t>-468</t>
+  </si>
+  <si>
+    <t>+681</t>
+  </si>
+  <si>
+    <t>+755</t>
+  </si>
+  <si>
+    <t>+1308</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>84.2%</t>
+  </si>
+  <si>
+    <t>7.4%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-7043</t>
-  </si>
-  <si>
-    <t>-1393</t>
-  </si>
-  <si>
-    <t>-755</t>
-  </si>
-  <si>
-    <t>+156</t>
-  </si>
-  <si>
-    <t>+169</t>
-  </si>
-  <si>
-    <t>+178</t>
-  </si>
-  <si>
-    <t>+1166</t>
+    <t>-533</t>
+  </si>
+  <si>
+    <t>+1251</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>81.2%</t>
-  </si>
-  <si>
-    <t>13.5%</t>
-  </si>
-  <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-432</t>
-  </si>
-  <si>
-    <t>+641</t>
-  </si>
-  <si>
-    <t>+2339</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>87.9%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-726</t>
-  </si>
-  <si>
-    <t>+1199</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+9900</t>
+    <t>46.9%</t>
+  </si>
+  <si>
+    <t>25.6%</t>
+  </si>
+  <si>
+    <t>15.3%</t>
+  </si>
+  <si>
+    <t>11.6%</t>
+  </si>
+  <si>
+    <t>+113</t>
+  </si>
+  <si>
+    <t>+291</t>
+  </si>
+  <si>
+    <t>+554</t>
+  </si>
+  <si>
+    <t>+762</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -625,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -653,7 +653,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -667,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -739,35 +739,35 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -778,10 +778,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -789,13 +789,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -806,66 +806,66 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -900,10 +900,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -911,41 +911,41 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -956,80 +956,80 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>Record</t>
   </si>
@@ -33,6 +33,9 @@
     <t>Sacks and the City</t>
   </si>
   <si>
+    <t>Hall Pass</t>
+  </si>
+  <si>
     <t>Big Ballsy Bozos</t>
   </si>
   <si>
@@ -42,109 +45,112 @@
     <t>Serving Punt</t>
   </si>
   <si>
-    <t>Hall Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hunks of Hanet </t>
   </si>
   <si>
+    <t>Natural rack</t>
+  </si>
+  <si>
     <t>Ler and Order</t>
   </si>
   <si>
-    <t>Natural rack</t>
-  </si>
-  <si>
     <t xml:space="preserve">Case Closed </t>
   </si>
   <si>
     <t xml:space="preserve">Jockstrap jubilee </t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>99.7%</t>
+    <t>98.7%</t>
   </si>
   <si>
     <t>93.6%</t>
   </si>
   <si>
-    <t>90.2%</t>
-  </si>
-  <si>
-    <t>82.4%</t>
-  </si>
-  <si>
-    <t>12.8%</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>7.1%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
+    <t>93.4%</t>
+  </si>
+  <si>
+    <t>87.9%</t>
+  </si>
+  <si>
+    <t>68.6%</t>
+  </si>
+  <si>
+    <t>49.3%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-33233</t>
+    <t>-7592</t>
   </si>
   <si>
     <t>-1462</t>
   </si>
   <si>
-    <t>-920</t>
-  </si>
-  <si>
-    <t>-468</t>
-  </si>
-  <si>
-    <t>+681</t>
-  </si>
-  <si>
-    <t>+755</t>
-  </si>
-  <si>
-    <t>+1308</t>
-  </si>
-  <si>
-    <t>+3604</t>
+    <t>-1415</t>
+  </si>
+  <si>
+    <t>-726</t>
+  </si>
+  <si>
+    <t>-218</t>
+  </si>
+  <si>
+    <t>+103</t>
+  </si>
+  <si>
+    <t>+1487</t>
+  </si>
+  <si>
+    <t>+6150</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>84.2%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
+    <t>67.0%</t>
+  </si>
+  <si>
+    <t>22.6%</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -153,43 +159,55 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-533</t>
-  </si>
-  <si>
-    <t>+1251</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>-203</t>
+  </si>
+  <si>
+    <t>+342</t>
+  </si>
+  <si>
+    <t>+2464</t>
+  </si>
+  <si>
+    <t>+2678</t>
+  </si>
+  <si>
+    <t>+5163</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>46.9%</t>
-  </si>
-  <si>
-    <t>25.6%</t>
-  </si>
-  <si>
-    <t>15.3%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
-  </si>
-  <si>
-    <t>+113</t>
-  </si>
-  <si>
-    <t>+291</t>
-  </si>
-  <si>
-    <t>+554</t>
-  </si>
-  <si>
-    <t>+762</t>
+    <t>66.0%</t>
+  </si>
+  <si>
+    <t>26.3%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-194</t>
+  </si>
+  <si>
+    <t>+280</t>
+  </si>
+  <si>
+    <t>+1371</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -611,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -625,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -639,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -653,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -667,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -739,12 +757,12 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -753,21 +771,21 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -775,13 +793,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -789,13 +807,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -803,13 +821,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -817,27 +835,27 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -845,27 +863,27 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -900,10 +918,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -914,38 +932,38 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -953,41 +971,41 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -998,38 +1016,38 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Record</t>
   </si>
@@ -36,21 +36,21 @@
     <t>Hall Pass</t>
   </si>
   <si>
+    <t>Serving Punt</t>
+  </si>
+  <si>
+    <t>Natural rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunks of Hanet </t>
+  </si>
+  <si>
     <t>Big Ballsy Bozos</t>
   </si>
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
   <si>
-    <t>Serving Punt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunks of Hanet </t>
-  </si>
-  <si>
-    <t>Natural rack</t>
-  </si>
-  <si>
     <t>Ler and Order</t>
   </si>
   <si>
@@ -60,154 +60,136 @@
     <t xml:space="preserve">Jockstrap jubilee </t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>98.7%</t>
-  </si>
-  <si>
-    <t>93.6%</t>
-  </si>
-  <si>
-    <t>93.4%</t>
-  </si>
-  <si>
-    <t>87.9%</t>
-  </si>
-  <si>
-    <t>68.6%</t>
-  </si>
-  <si>
-    <t>49.3%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>88.4%</t>
+  </si>
+  <si>
+    <t>76.7%</t>
+  </si>
+  <si>
+    <t>71.0%</t>
+  </si>
+  <si>
+    <t>67.4%</t>
+  </si>
+  <si>
+    <t>64.1%</t>
+  </si>
+  <si>
+    <t>34.9%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-762</t>
+  </si>
+  <si>
+    <t>-329</t>
+  </si>
+  <si>
+    <t>-245</t>
+  </si>
+  <si>
+    <t>-207</t>
+  </si>
+  <si>
+    <t>-179</t>
+  </si>
+  <si>
+    <t>+187</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>84.8%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-7592</t>
-  </si>
-  <si>
-    <t>-1462</t>
-  </si>
-  <si>
-    <t>-1415</t>
-  </si>
-  <si>
-    <t>-726</t>
-  </si>
-  <si>
-    <t>-218</t>
-  </si>
-  <si>
-    <t>+103</t>
-  </si>
-  <si>
-    <t>+1487</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-558</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+4248</t>
   </si>
   <si>
     <t>+16567</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>67.0%</t>
-  </si>
-  <si>
-    <t>22.6%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-203</t>
-  </si>
-  <si>
-    <t>+342</t>
-  </si>
-  <si>
-    <t>+2464</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+5163</t>
-  </si>
-  <si>
-    <t>+12400</t>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>66.0%</t>
-  </si>
-  <si>
-    <t>26.3%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-194</t>
-  </si>
-  <si>
-    <t>+280</t>
-  </si>
-  <si>
-    <t>+1371</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>24.6%</t>
+  </si>
+  <si>
+    <t>-298</t>
+  </si>
+  <si>
+    <t>+307</t>
   </si>
 </sst>
 </file>
@@ -629,7 +611,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -643,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -657,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -793,7 +775,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
@@ -804,10 +786,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
@@ -818,10 +800,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -832,24 +814,24 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
@@ -860,10 +842,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -874,7 +856,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -921,7 +903,7 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -935,7 +917,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -946,10 +928,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -960,29 +942,29 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -996,10 +978,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -1024,10 +1006,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>

--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
   <si>
     <t>Record</t>
   </si>
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Hunks of Hanet </t>
   </si>
   <si>
+    <t>Junya Ettlinger's First Team</t>
+  </si>
+  <si>
     <t>Big Ballsy Bozos</t>
   </si>
   <si>
-    <t>Junya Ettlinger's First Team</t>
-  </si>
-  <si>
     <t>Ler and Order</t>
   </si>
   <si>
@@ -60,136 +60,130 @@
     <t xml:space="preserve">Jockstrap jubilee </t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>88.4%</t>
-  </si>
-  <si>
-    <t>76.7%</t>
-  </si>
-  <si>
-    <t>71.0%</t>
-  </si>
-  <si>
-    <t>67.4%</t>
-  </si>
-  <si>
-    <t>64.1%</t>
-  </si>
-  <si>
-    <t>34.9%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>99.1%</t>
+  </si>
+  <si>
+    <t>96.4%</t>
+  </si>
+  <si>
+    <t>92.7%</t>
+  </si>
+  <si>
+    <t>63.9%</t>
+  </si>
+  <si>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>57.3%</t>
+  </si>
+  <si>
+    <t>28.0%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-2678</t>
+  </si>
+  <si>
+    <t>-1270</t>
+  </si>
+  <si>
+    <t>-177</t>
+  </si>
+  <si>
+    <t>-147</t>
+  </si>
+  <si>
+    <t>-134</t>
+  </si>
+  <si>
+    <t>+257</t>
+  </si>
+  <si>
+    <t>+3126</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>89.2%</t>
+  </si>
+  <si>
+    <t>7.9%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-762</t>
-  </si>
-  <si>
-    <t>-329</t>
-  </si>
-  <si>
-    <t>-245</t>
-  </si>
-  <si>
-    <t>-207</t>
-  </si>
-  <si>
-    <t>-179</t>
-  </si>
-  <si>
-    <t>+187</t>
-  </si>
-  <si>
-    <t>+14186</t>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-826</t>
+  </si>
+  <si>
+    <t>+1166</t>
+  </si>
+  <si>
+    <t>+3900</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>84.8%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
+    <t>92.5%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-558</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+4248</t>
+    <t>-1233</t>
+  </si>
+  <si>
+    <t>+1371</t>
   </si>
   <si>
     <t>+16567</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>74.9%</t>
-  </si>
-  <si>
-    <t>24.6%</t>
-  </si>
-  <si>
-    <t>-298</t>
-  </si>
-  <si>
-    <t>+307</t>
   </si>
 </sst>
 </file>
@@ -572,10 +566,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,10 +580,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,10 +594,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,10 +608,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,13 +619,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,13 +633,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -653,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -681,13 +675,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -695,13 +689,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -722,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -736,10 +730,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -750,10 +744,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -764,10 +758,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -778,94 +772,94 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -897,13 +891,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -911,13 +905,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -925,27 +919,27 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -953,13 +947,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -970,10 +964,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -984,10 +978,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -998,24 +992,24 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1026,10 +1020,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Operators Football League 2026 Betting Odds.xlsx
+++ b/data/odds/Operators Football League 2026 Betting Odds.xlsx
@@ -84,106 +84,106 @@
     <t>99.1%</t>
   </si>
   <si>
-    <t>96.4%</t>
-  </si>
-  <si>
-    <t>92.7%</t>
-  </si>
-  <si>
-    <t>63.9%</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>57.3%</t>
-  </si>
-  <si>
-    <t>28.0%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>92.4%</t>
+  </si>
+  <si>
+    <t>64.8%</t>
+  </si>
+  <si>
+    <t>56.2%</t>
+  </si>
+  <si>
+    <t>55.1%</t>
+  </si>
+  <si>
+    <t>33.0%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-1216</t>
+  </si>
+  <si>
+    <t>-184</t>
+  </si>
+  <si>
+    <t>-128</t>
+  </si>
+  <si>
+    <t>-123</t>
+  </si>
+  <si>
+    <t>+203</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>91.7%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-11011</t>
-  </si>
-  <si>
-    <t>-2678</t>
-  </si>
-  <si>
-    <t>-1270</t>
-  </si>
-  <si>
-    <t>-177</t>
-  </si>
-  <si>
-    <t>-147</t>
-  </si>
-  <si>
-    <t>-134</t>
-  </si>
-  <si>
-    <t>+257</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>89.2%</t>
-  </si>
-  <si>
-    <t>7.9%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-826</t>
-  </si>
-  <si>
-    <t>+1166</t>
-  </si>
-  <si>
-    <t>+3900</t>
+    <t>-1105</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+4900</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
-    <t>92.5%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-1233</t>
-  </si>
-  <si>
-    <t>+1371</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>92.3%</t>
+  </si>
+  <si>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>-1199</t>
+  </si>
+  <si>
+    <t>+1415</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
 </sst>
 </file>
@@ -780,13 +780,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -808,13 +808,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -828,7 +828,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -842,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -856,7 +856,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
@@ -930,21 +930,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -958,13 +958,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -972,13 +972,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -986,13 +986,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1020,7 +1020,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
